--- a/doc/source/_static/data/database_profiles/adb-71-economies-sets-7e96a2b0.xlsx
+++ b/doc/source/_static/data/database_profiles/adb-71-economies-sets-7e96a2b0.xlsx
@@ -1,12 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sets" sheetId="1" r:id="Ra838911a2b024804"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Readings" sheetId="2" r:id="R21ceb6d337054fd0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Regional memberships" sheetId="3" r:id="Rf23f71c9e98b4987"/>
-  </x:sheets>
-</x:workbook>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <sheets>
+    <sheet name="Sets" sheetId="1" r:id="Ra838911a2b024804"/>
+    <sheet name="Readings" sheetId="2" r:id="R21ceb6d337054fd0"/>
+    <sheet name="Regional memberships" sheetId="3" r:id="Rf23f71c9e98b4987"/>
+    <sheet name="Read me" sheetId="4" r:id="rId1"/>
+  </sheets>
+</workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
@@ -14,105 +15,166 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:numFmts count="3">
-    <x:numFmt numFmtId="200" formatCode="0"/>
-    <x:numFmt numFmtId="201" formatCode="@"/>
-    <x:numFmt numFmtId="202" formatCode="#,##0"/>
-  </x:numFmts>
-  <x:fonts count="5">
-    <x:font>
-      <x:sz val="11"/>
-      <x:name val="Carlito"/>
-    </x:font>
-    <x:font>
-      <x:b/>
-      <x:sz val="14"/>
-      <x:color rgb="FF202C38"/>
-      <x:name val="Arial"/>
-    </x:font>
-    <x:font>
-      <x:sz val="10"/>
-      <x:color rgb="FF566675"/>
-      <x:name val="Arial"/>
-    </x:font>
-    <x:font>
-      <x:sz val="10"/>
-      <x:color rgb="FF202C38"/>
-      <x:name val="Arial"/>
-    </x:font>
-    <x:font>
-      <x:b/>
-      <x:sz val="10"/>
-      <x:color rgb="FFFFFFFF"/>
-      <x:name val="Arial"/>
-    </x:font>
-  </x:fonts>
-  <x:fills count="3">
-    <x:fill>
-      <x:patternFill patternType="none"/>
-    </x:fill>
-    <x:fill>
-      <x:patternFill patternType="gray125"/>
-    </x:fill>
-    <x:fill>
-      <x:patternFill patternType="solid">
-        <x:fgColor rgb="FF245B6A"/>
-      </x:patternFill>
-    </x:fill>
-  </x:fills>
-  <x:borders count="1">
-    <x:border>
-      <x:left/>
-      <x:right/>
-      <x:top/>
-      <x:bottom/>
-      <x:diagonal/>
-    </x:border>
-  </x:borders>
-  <x:cellStyleXfs count="1">
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-  </x:cellStyleXfs>
-  <x:cellXfs count="14">
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center" wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="200" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="201" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="201" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center" wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="202" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center" wrapText="1"/>
-    </x:xf>
-  </x:cellXfs>
-  <x:cellStyles count="1">
-    <x:cellStyle name="Normal" xfId="0"/>
-  </x:cellStyles>
-</x:styleSheet>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="4">
+    <numFmt numFmtId="200" formatCode="0"/>
+    <numFmt numFmtId="201" formatCode="@"/>
+    <numFmt numFmtId="202" formatCode="#,##0"/>
+    <numFmt numFmtId="203" formatCode="@"/>
+  </numFmts>
+  <fonts count="9">
+    <font>
+      <sz val="11"/>
+      <name val="Carlito"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <color rgb="FF202C38"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF566675"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF202C38"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Carlito"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF302820"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FF302820"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Arial"/>
+    </font>
+  </fonts>
+  <fills count="6">
+    <fill>
+      <patternFill patternType="none"/>
+    </fill>
+    <fill>
+      <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF245B6A"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="none"/>
+    </fill>
+    <fill>
+      <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF302820"/>
+      </patternFill>
+    </fill>
+  </fills>
+  <borders count="2">
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+  </borders>
+  <cellStyleXfs count="2">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1"/>
+  </cellStyleXfs>
+  <cellXfs count="22">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="200" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="201" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="201" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="202" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="1"/>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="203" fontId="6" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+  </cellXfs>
+  <cellStyles count="1">
+    <cellStyle name="Normal" xfId="0"/>
+  </cellStyles>
+</styleSheet>
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -35165,4 +35227,108 @@
     <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R15697fd2e6d04989"/>
   </x:tableParts>
 </x:worksheet>
+</file>
+
+<file path=xl/worksheets/source_notice4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="FFF0783C"/>
+  </sheetPr>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="22" hidden="0" customWidth="1"/>
+    <col min="2" max="2" width="100" hidden="0" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="16.799999237060547" hidden="0" customHeight="1">
+      <c r="A1" s="20" t="str">
+        <v>Read me</v>
+      </c>
+      <c r="B1" s="20" t="str">
+        <v>ADB · 71 economies · economic accounts</v>
+      </c>
+    </row>
+    <row r="2" ht="15" hidden="0" customHeight="1">
+      <c r="A2" s="18" t="str">
+        <v>Contents</v>
+      </c>
+      <c r="B2" s="21" t="str">
+        <v>Native set labels and units. No economic observations, emission factors or coefficients.</v>
+      </c>
+    </row>
+    <row r="3" ht="15" hidden="0" customHeight="1">
+      <c r="A3" s="18" t="str">
+        <v>Verified years</v>
+      </c>
+      <c r="B3" s="21" t="str">
+        <v>2007, 2011, 2017</v>
+      </c>
+    </row>
+    <row r="4" ht="15" hidden="0" customHeight="1">
+      <c r="A4" s="18" t="str">
+        <v>How to use</v>
+      </c>
+      <c r="B4" s="21" t="str">
+        <v>Read Sets (or the named set tabs) for labels and units; Readings identifies source years. Identical inventories do not imply identical numerical results.</v>
+      </c>
+    </row>
+    <row r="5" ht="15" hidden="0" customHeight="1">
+      <c r="A5" s="18" t="str">
+        <v>Source</v>
+      </c>
+      <c r="B5" s="21" t="str">
+        <v>https://www.adb.org/what-we-do/data/regional-input-output-tables</v>
+      </c>
+    </row>
+    <row r="6" ht="15" hidden="0" customHeight="1">
+      <c r="A6" s="18" t="str">
+        <v>Attribution</v>
+      </c>
+      <c r="B6" s="21" t="str">
+        <v>Asian Development Bank</v>
+      </c>
+    </row>
+    <row r="7" ht="15" hidden="0" customHeight="1">
+      <c r="A7" s="18" t="str">
+        <v>Source terms</v>
+      </c>
+      <c r="B7" s="21" t="str">
+        <v>ADB Key Indicators data terms</v>
+      </c>
+    </row>
+    <row r="8" ht="15" hidden="0" customHeight="1">
+      <c r="A8" s="18" t="str">
+        <v>Terms URL</v>
+      </c>
+      <c r="B8" s="21" t="str">
+        <v>https://kidb.adb.org/terms</v>
+      </c>
+    </row>
+    <row r="9" ht="24" hidden="0" customHeight="1">
+      <c r="A9" s="18" t="str">
+        <v>Reuse</v>
+      </c>
+      <c r="B9" s="21" t="str">
+        <v>Credit ADB and the original dataset. Check the terms attached to the downloaded MRIO release; ADB Data Library has a separate CC BY 3.0 IGO policy.</v>
+      </c>
+    </row>
+    <row r="10" ht="15" hidden="0" customHeight="1">
+      <c r="A10" s="18" t="str">
+        <v>Changes</v>
+      </c>
+      <c r="B10" s="21" t="str">
+        <v>Extracted and arranged with MARIO. Native labels and units are retained. Country names and ISO matches are documentation metadata.</v>
+      </c>
+    </row>
+    <row r="11" ht="15" hidden="0" customHeight="1">
+      <c r="A11" s="18" t="str">
+        <v>Limit</v>
+      </c>
+      <c r="B11" s="21" t="str">
+        <v>A set inventory describes the parsed input, not the quality of the source or a licence to use its numerical data.</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>